--- a/depin/content/faq-0830.xlsx
+++ b/depin/content/faq-0830.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>wellbian FAQ 정본 — 2026-08-30 개정</t>
+          <t>wellbian FAQ 정본 — 2026-08-30 1차 확정</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>8/30 회의 결정 + 라이브 사이트(wlbn.wellbianlabs.io) + CS 대시보드가 모은 미답변 질문</t>
+          <t>8/30 회의 결정 + 라이브 사이트(wlbn.wellbianlabs.io) + CS 대시보드가 모은 미답변 질문 + 8/30 서우 1차 확정본</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>9월 7일 정오에 열리는 구매 예약입니다. 결제가 아니고 비용도 들지 않습니다. 신청하시면 지갑으로 예매권 NFT가 발급되고, 이 NFT를 가진 분에게 9월 15일 정오 우선 구매창이 먼저 열립니다.</t>
+          <t>9월 7일 정오에 열리는 구매 예약입니다. 결제가 아니며 저희에게 내시는 금액은 없습니다. 신청하시면 지갑으로 예매권 NFT가 발급되고, 이 NFT를 가진 분에게 9월 15일 정오 우선 구매창이 먼저 열립니다.</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>A reservation that opens at noon on September 7. It is not a payment and costs nothing. When you apply, a reservation NFT is issued to your wallet, and holders of that NFT get the priority purchase window first, at noon on September 15.</t>
+          <t>A reservation that opens at noon on September 7. It is not a payment, and you pay us nothing. When you apply, a reservation NFT is issued to your wallet, and holders of that NFT get the priority purchase window first, at noon on September 15.</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>지갑 주소와 계정 아이디만 입력하시면 됩니다. 그 밖의 정보는 받지 않습니다. 신청 후 지갑으로 오는 예매권 NFT를 수락하시면 예약이 확정됩니다.</t>
+          <t>지갑 주소로 로그인하시거나 구글 계정으로 로그인하시면 됩니다. 그 밖의 정보는 받지 않습니다. 지갑에 최소 1.5 XRP 이상이 있어야 예매권 NFT를 받으실 수 있습니다 — XRPL 지갑을 만들고 트러스트라인을 여는 데 드는 네트워크 준비금입니다. 신청 후 지갑으로 오는 예매권 NFT를 수락하시면 예약이 확정됩니다.</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>Enter your wallet address and account ID — nothing else is collected. Accept the reservation NFT that arrives in your wallet and your reservation is confirmed.</t>
+          <t>Sign in with your wallet address or with a Google account — nothing else is collected. Your wallet needs at least 1.5 XRP to receive the reservation NFT — the network reserve required to create an XRPL wallet and open a trustline. Accept the reservation NFT that arrives in your wallet and your reservation is confirmed.</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>구매를 보장하지는 않습니다. 예매권을 가진 분에게 구매창이 먼저 열리는 것이고, 신청이 준비된 물량을 넘으면 선착순이 아니라 추첨으로 정합니다. 예약 자체에는 비용이 들지 않습니다.</t>
+          <t>구매를 보장하지는 않습니다. 예매권을 가진 분에게 구매창이 먼저 열리는 것이고, 신청이 준비된 물량을 넘으면 선착순이 아니라 추첨으로 정합니다. 예약으로 저희에게 내시는 금액은 없습니다.</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>It does not guarantee a purchase. Reservation holders simply get the window first, and if applications exceed the prepared quantity, allocation is by draw rather than first-come. Reserving itself costs nothing.</t>
+          <t>It does not guarantee a purchase. Reservation holders simply get the window first, and if applications exceed the prepared quantity, allocation is by draw rather than first-come. Reserving itself costs you nothing on our side.</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>1계정당 최대 10대까지 신청하실 수 있습니다. 기업이나 대량 구매는 별도 문의로 안내드립니다.</t>
+          <t>1계정당 최대 10대까지 신청하실 수 있습니다. 기업이나 대량 구매는 admin@wellbianlab.io 로 문의해 주세요.</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Up to 10 per account. For business or bulk purchases, please contact us separately.</t>
+          <t>Up to 10 per account. For business or bulk purchases, contact admin@wellbianlab.io.</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>괜찮습니다. 계정을 만들면 기본 지갑이 자동으로 생성되고, 이미 쓰시는 지갑이 있으면 연결해서 쓰셔도 됩니다. XRP는 일부 지갑과 호환되지 않으니 XRPL을 지원하는 지갑을 쓰셔야 합니다. 단계별로 안내해 드립니다.</t>
+          <t>괜찮습니다. 계정을 만들면 기본 지갑이 자동으로 생성되고, 이미 쓰시는 지갑이 있으면 연결해서 쓰셔도 됩니다. XRP는 일부 지갑과 호환되지 않으니 XRPL을 지원하는 지갑을 쓰셔야 합니다. 단계별로 안내해 드립니다. 지갑에 최소 1.5 XRP 이상이 있어야 예매권 NFT를 받으실 수 있습니다 — XRPL 지갑을 만들고 트러스트라인을 여는 데 드는 네트워크 준비금입니다.</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Not at all. Creating an account generates a wallet for you, and you can connect one you already use instead. XRP is not compatible with every wallet, so use one that supports XRPL. We guide you step by step.</t>
+          <t>Not at all. Creating an account generates a wallet for you, and you can connect one you already use instead. XRP is not compatible with every wallet, so use one that supports XRPL. We guide you step by step. Your wallet needs at least 1.5 XRP to receive the reservation NFT — the network reserve required to create an XRPL wallet and open a trustline.</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>사전예약에는 비용이 들지 않으므로 환불할 금액이 없습니다. 언제든 예약을 하지 않으셔도 됩니다. 구매 후의 환불은 판매 약관에 따르며, 약관은 판매 오픈 전에 공지됩니다.</t>
+          <t>사전예약으로 저희에게 내신 금액이 없으므로 환불해 드릴 것도 없습니다. 언제든 예약을 하지 않으셔도 됩니다. 지갑에 넣어 두신 XRP는 저희에게 오는 돈이 아니라 계정에 남는 네트워크 준비금입니다. 구매 후의 환불은 판매 약관에 따르며, 약관은 판매 오픈 전에 공지됩니다.</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Pre-reservation costs nothing, so there is nothing to refund — you are free to walk away at any point. Refunds after purchase follow the sale terms, which are published before the sale opens.</t>
+          <t>You pay us nothing to pre-reserve, so there is nothing for us to refund — you are free to walk away at any point. The XRP you keep in your wallet is not paid to us; it stays in your account as a network reserve. Refunds after purchase follow the sale terms, which are published before the sale opens.</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>XRPL에서 내 지갑이 특정 토큰을 받겠다고 여는 통로입니다. RLUSD를 받으려면 필요하고, 결제 단계에서 자동으로 점검해 드리니 따로 하실 일은 없습니다.</t>
+          <t>XRPL에서 내 지갑이 특정 토큰을 받겠다고 여는 통로입니다. RLUSD를 받으려면 필요하고, 결제 단계에서 자동으로 점검해 드립니다. 트러스트라인을 열 때 XRP 준비금이 계정에 잡히는데, 이는 저희에게 오는 돈이 아니라 지갑에 남는 금액입니다.</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>On the XRPL it is the channel your wallet opens to accept a given token. You need one to receive RLUSD, and we check it automatically during payment — nothing for you to do.</t>
+          <t>On the XRPL it is the channel your wallet opens to accept a given token. You need one to receive RLUSD, and we check it automatically during payment. Opening a trustline locks a small XRP reserve in your account — that is not paid to us; it stays in your wallet.</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>실내 공기질 측정기 ARC-600DA입니다. CO₂·미세먼지·온습도를 측정하고 KC 인증과 성능 인증을 받았습니다. 자세한 사양은 사이트의 제품 스펙에서 보실 수 있습니다.</t>
+          <t>실내 공기질 측정기 ARC-600DA입니다. CO₂·미세먼지·온습도를 측정하고 대한민국 KC 인증과 성능 인증을 받았습니다. 자세한 사양은 사이트의 제품 스펙에서 보실 수 있습니다.</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>The ARC-600DA indoor air quality monitor. It measures CO₂, particulates, temperature and humidity, and carries KC certification and performance certification. Full specifications are on the site.</t>
+          <t>The ARC-600DA indoor air quality monitor. It measures CO₂, particulates, temperature and humidity, and carries Korean KC certification and performance certification. Full specifications are on the site.</t>
         </is>
       </c>
     </row>
@@ -3164,22 +3164,22 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>기업·대량 문의 창구</t>
+          <t>문의 도메인 표기</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>미정</t>
+          <t>admin@wellbianlab.io</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>b3 이 '별도 문의' 라고만 안내한다. 받을 곳이 필요</t>
+          <t>사이트 도메인은 wellbianlabs.io(s 있음)인데 확정본 메일은 wellbianlab.io(s 없음)다. 둘 중 하나가 오타면 대량 구매 문의를 통째로 잃는다</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>9/7 전</t>
+          <t>즉시</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -3496,7 +3496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3645,17 +3645,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>입력 항목</t>
+          <t>로그인 방식</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>지갑 주소 + 계정 아이디</t>
+          <t>지갑 주소 로그인 또는 구글 로그인</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>8/30 회의</t>
+          <t>8/30 서우 확정</t>
         </is>
       </c>
     </row>
@@ -3667,188 +3667,188 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>예매 증표</t>
+          <t>NFT 수령 조건</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>예매권 NFT (지갑 발급)</t>
+          <t>지갑에 최소 1.5 XRP — XRPL 계정 생성·트러스트라인 준비금 (저희에게 오는 금액이 아님)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>8/30 회의 · 사이트</t>
+          <t>8/30 서우 확정</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>예매</t>
+          <t>문의</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>물량 초과 시</t>
+          <t>기업·대량 구매</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>선착순 아닌 추첨</t>
+          <t>admin@wellbianlab.io</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>8/30 회의</t>
+          <t>8/30 서우 확정 — 도메인 표기 확인 필요</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>결제</t>
+          <t>예매</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>결제 수단</t>
+          <t>예매 증표</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>RLUSD (달러 1:1 · 리플 발행)</t>
+          <t>예매권 NFT (지갑 발급)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>사이트</t>
+          <t>8/30 회의 · 사이트</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>결제</t>
+          <t>예매</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>출금 네트워크</t>
+          <t>물량 초과 시</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>XRPL — 다른 네트워크 선택 시 자산 손실</t>
+          <t>선착순 아닌 추첨</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>사이트</t>
+          <t>8/30 회의</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>지갑</t>
+          <t>결제</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>지원 경로</t>
+          <t>결제 수단</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>기본 지갑 자동 생성 · 외부 지갑 연결</t>
+          <t>RLUSD (달러 1:1 · 리플 발행)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>8/30 회의</t>
+          <t>사이트</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>지갑</t>
+          <t>결제</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>XRP 호환</t>
+          <t>출금 네트워크</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>메타마스크 비호환 · XRPL 지원 지갑 필요</t>
+          <t>XRPL — 다른 네트워크 선택 시 자산 손실</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>8/30 회의</t>
+          <t>사이트</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>NFT</t>
+          <t>지갑</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>관측소 TAXON</t>
+          <t>지원 경로</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>1001 제네시스 · 1002 지역 한정 · 1003 사업 한정 (계정당 1개)</t>
+          <t>기본 지갑 자동 생성 · 외부 지갑 연결</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>사이트</t>
+          <t>8/30 회의</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>NFT</t>
+          <t>지갑</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>스테이션 TAXON</t>
+          <t>XRP 호환</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>3026 실내 · 2026 실외 · 4026 AI인프라 · 5026 레이다 · 6026 위성 (기기당 1개)</t>
+          <t>메타마스크 비호환 · XRPL 지원 지갑 필요</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>사이트</t>
+          <t>8/30 회의</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>토큰</t>
+          <t>NFT</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>표준</t>
+          <t>관측소 TAXON</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>XRPL 발행 자산(IOU) · XLS-20 / XLS-30</t>
+          <t>1001 제네시스 · 1002 지역 한정 · 1003 사업 한정 (계정당 1개)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -3860,17 +3860,17 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>토큰</t>
+          <t>NFT</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>총 발행량</t>
+          <t>스테이션 TAXON</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>1,000,000 (고정)</t>
+          <t>3026 실내 · 2026 실외 · 4026 AI인프라 · 5026 레이다 · 6026 위성 (기기당 1개)</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>소각</t>
+          <t>표준</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>데이터 판매 시 결제액의 50% 영구 소각</t>
+          <t>XRPL 발행 자산(IOU) · XLS-20 / XLS-30</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -3904,17 +3904,17 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>토큰</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>예산 방식</t>
+          <t>총 발행량</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>에폭(1일) 단위 고정 예산 · 품질 점수 기여도로 배분</t>
+          <t>1,000,000 (고정)</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -3926,17 +3926,17 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>토큰</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>기기당 상한</t>
+          <t>소각</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>일 예산의 0.5%</t>
+          <t>데이터 판매 시 결제액의 50% 영구 소각</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>기기 배수</t>
+          <t>예산 방식</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>ARC-600DA = 기준 1.0</t>
+          <t>에폭(1일) 단위 고정 예산 · 품질 점수 기여도로 배분</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -3975,34 +3975,34 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>수령 조건</t>
+          <t>기기당 상한</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>기기 라이선스 NFT 발급</t>
+          <t>일 예산의 0.5%</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>8/30 회의 · 사이트</t>
+          <t>사이트</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>개인정보</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>비식별화</t>
+          <t>기기 배수</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>위치 일반화 · 시간 집계 · 식별자 회전 · k-익명성 · 속성 일반화</t>
+          <t>ARC-600DA = 기준 1.0</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -4014,39 +4014,39 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>개인정보</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>응답 단위</t>
+          <t>수령 조건</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>개별 기기가 아닌 코호트 통계</t>
+          <t>기기 라이선스 NFT 발급</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>사이트</t>
+          <t>8/30 회의 · 사이트</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>기기</t>
+          <t>개인정보</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>모델</t>
+          <t>비식별화</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>ARC-600DA 실내 공기질 측정기</t>
+          <t>위치 일반화 · 시간 집계 · 식별자 회전 · k-익명성 · 속성 일반화</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -4058,17 +4058,17 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>기기</t>
+          <t>개인정보</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>측정 항목</t>
+          <t>응답 단위</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>CO₂ · 미세먼지 · 온습도</t>
+          <t>개별 기기가 아닌 코호트 통계</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -4085,17 +4085,61 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>ARC-600DA 실내 공기질 측정기</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>사이트</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>기기</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>측정 항목</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>CO₂ · 미세먼지 · 온습도</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>사이트</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>기기</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
           <t>인증</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>KC 인증 · 성능 인증</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>사이트</t>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>대한민국 KC 인증 · 성능 인증</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>8/30 서우 확정</t>
         </is>
       </c>
     </row>

--- a/depin/content/faq-0830.xlsx
+++ b/depin/content/faq-0830.xlsx
@@ -836,7 +836,7 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>1계정당 최대 10대까지 신청하실 수 있습니다. 기업이나 대량 구매는 admin@wellbianlab.io 로 문의해 주세요.</t>
+          <t>1계정당 최대 10대까지 신청하실 수 있습니다. 기업이나 대량 구매는 admin@wellbian.io 로 문의해 주세요.</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Up to 10 per account. For business or bulk purchases, contact admin@wellbianlab.io.</t>
+          <t>Up to 10 per account. For business or bulk purchases, email admin@wellbian.io — we handle those separately.</t>
         </is>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3164,22 +3164,22 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>문의 도메인 표기</t>
+          <t>기기 판매처</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>admin@wellbianlab.io</t>
+          <t>이 사이트 / KWeather 몰</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>사이트 도메인은 wellbianlabs.io(s 있음)인데 확정본 메일은 wellbianlab.io(s 없음)다. 둘 중 하나가 오타면 대량 구매 문의를 통째로 잃는다</t>
+          <t>옛 정본은 '기기는 KWeather 몰' 이라 했으나 사이트는 기기를 판다. 개정본에서는 뺐다</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>즉시</t>
+          <t>9/7 전</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -3189,51 +3189,51 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>기기 판매처</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>이 사이트 / KWeather 몰</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>옛 정본은 '기기는 KWeather 몰' 이라 했으나 사이트는 기기를 판다. 개정본에서는 뺐다</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>9/7 전</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>높음</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>2년 정확도 점검</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>근거 조항 미확인</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>미세먼지 특별법 조항을 찾아 약관에 넣기로 함. 확정되면 FAQ 문항 추가</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>9/15 전</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>중간</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>2년 정확도 점검</t>
+          <t>국내 거래소 지원 현황</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>근거 조항 미확인</t>
+          <t>코인원·디센트만 확인</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>미세먼지 특별법 조항을 찾아 약관에 넣기로 함. 확정되면 FAQ 문항 추가</t>
+          <t>b7 이 일반론으로 답한다. 거래소별 표를 줄 수 있으면 문의가 크게 준다</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>9/15 전</t>
+          <t>9/7 전</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -3245,22 +3245,22 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>국내 거래소 지원 현황</t>
+          <t>마이페이지 명칭</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>코인원·디센트만 확인</t>
+          <t>→ 데이터 보상</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>b7 이 일반론으로 답한다. 거래소별 표를 줄 수 있으면 문의가 크게 준다</t>
+          <t>회의 지시. 화면 문구와 FAQ 표현을 함께 바꿔야 한다</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>9/7 전</t>
+          <t>9/15 전</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -3272,17 +3272,17 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>마이페이지 명칭</t>
+          <t>보상 시작 시점</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>→ 데이터 보상</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>회의 지시. 화면 문구와 FAQ 표현을 함께 바꿔야 한다</t>
+          <t>'언제부터 받나요' 가 자주 나올 텐데 b9 는 조건만 답한다</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -3299,17 +3299,17 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>보상 시작 시점</t>
+          <t>제네시스 부스트 배수</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>미정</t>
+          <t>미공개</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>'언제부터 받나요' 가 자주 나올 텐데 b9 는 조건만 답한다</t>
+          <t>x2 는 '보상 부스트' 라고만 쓴다. 수치를 낼지 결정</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -3319,78 +3319,78 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>낮음</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>제네시스 부스트 배수</t>
+          <t>예매권 미수락 처리</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>미공개</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>x2 는 '보상 부스트' 라고만 쓴다. 수치를 낼지 결정</t>
+          <t>마감까지 수락하지 않은 예매권을 어떻게 할지</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>9/15 전</t>
+          <t>9/14 전</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>낮음</t>
+          <t>중간</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>예매권 미수락 처리</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>마감까지 수락하지 않은 예매권을 어떻게 할지</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>9/14 전</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>중간</t>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>지갑 키 보관 주체</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>자동 생성 지갑의 개인키를 누가 갖는지. 자산 관리 주체라 반드시 답이 있어야 하고, 답에 따라 문항 문안이 크게 달라진다</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>9/7 전</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>지갑 키 보관 주체</t>
+          <t>신청 후 수량 변경·취소</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>자동 생성 지갑의 개인키를 누가 갖는지. 자산 관리 주체라 반드시 답이 있어야 하고, 답에 따라 문항 문안이 크게 달라진다</t>
+          <t>마감 전에 바꿀 수 있는지. 못 바꾸면 신청 화면에서 미리 알려야 한다</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -3405,81 +3405,54 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>신청 후 수량 변경·취소</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>마감 전에 바꿀 수 있는지. 못 바꾸면 신청 화면에서 미리 알려야 한다</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>출금 수수료·소요 시간</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>거래소마다 상이</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>일반론만 답할 수 있다. 주요 거래소 기준값이 있으면 문의가 준다</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>9/7 전</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>높음</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>낮음</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>출금 수수료·소요 시간</t>
+          <t>실외·위성 기기 로드맵</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>거래소마다 상이</t>
+          <t>비공개</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>일반론만 답할 수 있다. 주요 거래소 기준값이 있으면 문의가 준다</t>
+          <t>TAXON 표에는 이미 있다. 물어보면 어디까지 답할지</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>9/7 전</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>실외·위성 기기 로드맵</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>비공개</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>TAXON 표에는 이미 있다. 물어보면 어디까지 답할지</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>낮음</t>
         </is>
@@ -3694,12 +3667,12 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>admin@wellbianlab.io</t>
+          <t>admin@wellbian.io</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>8/30 서우 확정 — 도메인 표기 확인 필요</t>
+          <t>8/30 서우 확정</t>
         </is>
       </c>
     </row>

--- a/depin/content/faq-0830.xlsx
+++ b/depin/content/faq-0830.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>wellbian FAQ 정본 — 2026-08-30 1차 확정</t>
+          <t>wellbian FAQ 정본 — 2026-08-30 1차 확정 (2차 보강)</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>기본 10 · 확장 14 · 합계 24 (KO·EN 동일)</t>
+          <t>기본 10 · 확장 16 · 합계 26 (KO·EN 동일)</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1590,6 +1590,80 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>x14</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>예매</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>신청한 뒤에 수량을 바꾸거나 취소할 수 있나요?</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>신청 후에는 수량을 바꾸거나 취소하실 수 없습니다. 신청은 수요를 가늠하기 위한 것이라 구매 의무가 아니고, 실제 구매는 우선 구매창에서 원하시는 만큼만 하시면 되므로 굳이 바꾸실 필요도 없습니다.</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Can I change or cancel my reservation after applying?</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>Reservations cannot be changed or cancelled once submitted. Applying is how we gauge demand, not a commitment to buy — and since you can take as few as you like in the purchase window, there is no need to change it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>x15</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>지갑</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>구글로 만든 지갑을 다른 지갑으로 옮길 수 있나요?</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>구글 계정으로 만든 지갑은 니모닉이나 개인키를 내보내 다른 지갑으로 옮기실 수 없습니다. 그 지갑에 있는 NFT를 다른 곳으로 두시려면 외부 개인 지갑을 연결하신 뒤 그 지갑으로 전송하시면 됩니다.</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Can I move the wallet created with Google to another wallet?</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>A wallet created with a Google account cannot be exported — there is no mnemonic or private key to move elsewhere. To hold its NFT somewhere else, connect an external personal wallet and transfer the NFT to it.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1601,7 +1675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2717,7 +2791,7 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>b1</t>
+          <t>x14</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -2730,21 +2804,17 @@
           <t>예매</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr">
-        <is>
-          <t>※ 문항 없음 — 변경·취소 가능 여부 미정</t>
-        </is>
-      </c>
+      <c r="D61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>b1</t>
+          <t>x14</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>마감 직전에 신청해도 되나요</t>
+          <t>신청 취소하고 싶어요</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
@@ -2752,65 +2822,53 @@
           <t>예매</t>
         </is>
       </c>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>추첨이므로 순서는 무관 — b2 가 받는다</t>
-        </is>
-      </c>
+      <c r="D62" s="8" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>b1</t>
+          <t>x15</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>먼저 신청하면 유리한가요</t>
+          <t>구글로 만든 지갑 니모닉 알려주세요</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>예매</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>b2 가 받는다</t>
-        </is>
-      </c>
+          <t>지갑</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>b0</t>
+          <t>x15</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>예매권은 어디서 수락하나요</t>
+          <t>지갑을 메타마스크로 옮길 수 있나요</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>예매</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>※ 문항 없음 — 수락 화면 확정 후 추가</t>
-        </is>
-      </c>
+          <t>지갑</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>b0</t>
+          <t>b1</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>수락 기한이 있나요</t>
+          <t>마감 직전에 신청해도 되나요</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
@@ -2820,159 +2878,225 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>※ 문항 없음 — 미수락 처리 미정</t>
+          <t>추첨이므로 순서는 무관 — b2 가 받는다</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>b4</t>
+          <t>b1</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>일반 구매창이 더 일찍 열린다는 게 무슨 뜻인가요</t>
+          <t>먼저 신청하면 유리한가요</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>일정</t>
+          <t>예매</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>b4 에 조건이 들어 있으나 풀어 쓸지 검토</t>
+          <t>b2 가 받는다</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>b8</t>
+          <t>b0</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>자동으로 만들어진 지갑은 누가 관리하나요</t>
+          <t>예매권은 어디서 수락하나요</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>지갑</t>
+          <t>예매</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>※ 문항 없음 — 키 보관 주체 확인 필요. 자주 나올 질문</t>
+          <t>※ 문항 없음 — 수락 화면 확정 후 추가</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>b8</t>
+          <t>b0</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>개인키는 제가 갖는 건가요</t>
+          <t>수락 기한이 있나요</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>지갑</t>
+          <t>예매</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>※ 문항 없음 — 같은 사안</t>
+          <t>※ 문항 없음 — 미수락 처리 미정</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>b6</t>
+          <t>b4</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>출금 수수료와 도착까지 걸리는 시간은요</t>
+          <t>일반 구매창이 더 일찍 열린다는 게 무슨 뜻인가요</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>결제</t>
+          <t>일정</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>※ 문항 없음 — 거래소마다 달라 일반론만 가능</t>
+          <t>b4 에 조건이 들어 있으나 풀어 쓸지 검토</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>b6</t>
+          <t>x15</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>얼마를 준비해야 하나요</t>
+          <t>자동으로 만들어진 지갑은 누가 관리하나요</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>결제</t>
+          <t>지갑</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>가격 확정 전까지 b5 가 받는다</t>
+          <t>x15 가 내보내기 불가를 답한다</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>x2</t>
+          <t>x15</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>멤버십을 사면 측정기도 같이 오나요</t>
+          <t>개인키는 제가 갖는 건가요</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>멤버십</t>
+          <t>지갑</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>※ 문항 없음 — 기기 판매처 결정에 달림</t>
+          <t>x15 가 받는다</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
+          <t>b6</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>출금 수수료와 도착까지 걸리는 시간은요</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>결제</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>※ 문항 없음 — 거래소마다 달라 일반론만 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>b6</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>얼마를 준비해야 하나요</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>결제</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>가격 확정 전까지 b5 가 받는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>x2</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>멤버십을 사면 측정기도 같이 오나요</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>멤버십</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>※ 문항 없음 — 기기 판매처 결정에 달림</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
           <t>x3</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>우선창에서 제가 예매자인 걸 어떻게 확인하나요</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>멤버십</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>※ 문항 없음 — 확인 화면 확정 후</t>
         </is>
@@ -2989,7 +3113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3351,108 +3475,81 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>지갑 키 보관 주체</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>미확인</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>자동 생성 지갑의 개인키를 누가 갖는지. 자산 관리 주체라 반드시 답이 있어야 하고, 답에 따라 문항 문안이 크게 달라진다</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>지갑 수탁 주체 표기</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>사용자 답변은 확정</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>내보내기 불가·외부 지갑 연동으로 이전한다는 답은 확정됐다. 약관에 수탁 주체를 어떻게 적을지는 남았다</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>9/15 전</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>출금 수수료·소요 시간</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>거래소마다 상이</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>일반론만 답할 수 있다. 주요 거래소 기준값이 있으면 문의가 준다</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>9/7 전</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>신청 후 수량 변경·취소</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>마감 전에 바꿀 수 있는지. 못 바꾸면 신청 화면에서 미리 알려야 한다</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>9/7 전</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>높음</t>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>낮음</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>출금 수수료·소요 시간</t>
+          <t>실외·위성 기기 로드맵</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>거래소마다 상이</t>
+          <t>비공개</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>일반론만 답할 수 있다. 주요 거래소 기준값이 있으면 문의가 준다</t>
+          <t>TAXON 표에는 이미 있다. 물어보면 어디까지 답할지</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>9/7 전</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>실외·위성 기기 로드맵</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>비공개</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>TAXON 표에는 이미 있다. 물어보면 어디까지 답할지</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>낮음</t>
         </is>
@@ -3469,7 +3566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3723,149 +3820,149 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>결제</t>
+          <t>예매</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>결제 수단</t>
+          <t>신청 후 변경·취소</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>RLUSD (달러 1:1 · 리플 발행)</t>
+          <t>불가 — 수요 예측용이며 구매 의무가 아니다</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>사이트</t>
+          <t>8/30 서우 확정</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>결제</t>
+          <t>지갑</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>출금 네트워크</t>
+          <t>구글 생성 지갑</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>XRPL — 다른 네트워크 선택 시 자산 손실</t>
+          <t>니모닉·개인키 내보내기 불가. NFT 이전은 외부 개인 지갑을 연동해 전송</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>사이트</t>
+          <t>8/30 서우 확정</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>지갑</t>
+          <t>결제</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>지원 경로</t>
+          <t>결제 수단</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>기본 지갑 자동 생성 · 외부 지갑 연결</t>
+          <t>RLUSD (달러 1:1 · 리플 발행)</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>8/30 회의</t>
+          <t>사이트</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>지갑</t>
+          <t>결제</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>XRP 호환</t>
+          <t>출금 네트워크</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>메타마스크 비호환 · XRPL 지원 지갑 필요</t>
+          <t>XRPL — 다른 네트워크 선택 시 자산 손실</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>8/30 회의</t>
+          <t>사이트</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>NFT</t>
+          <t>지갑</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>관측소 TAXON</t>
+          <t>지원 경로</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>1001 제네시스 · 1002 지역 한정 · 1003 사업 한정 (계정당 1개)</t>
+          <t>기본 지갑 자동 생성 · 외부 지갑 연결</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>사이트</t>
+          <t>8/30 회의</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>NFT</t>
+          <t>지갑</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>스테이션 TAXON</t>
+          <t>XRP 호환</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>3026 실내 · 2026 실외 · 4026 AI인프라 · 5026 레이다 · 6026 위성 (기기당 1개)</t>
+          <t>메타마스크 비호환 · XRPL 지원 지갑 필요</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>사이트</t>
+          <t>8/30 회의</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>토큰</t>
+          <t>NFT</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>표준</t>
+          <t>관측소 TAXON</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>XRPL 발행 자산(IOU) · XLS-20 / XLS-30</t>
+          <t>1001 제네시스 · 1002 지역 한정 · 1003 사업 한정 (계정당 1개)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -3877,17 +3974,17 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>토큰</t>
+          <t>NFT</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>총 발행량</t>
+          <t>스테이션 TAXON</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>1,000,000 (고정)</t>
+          <t>3026 실내 · 2026 실외 · 4026 AI인프라 · 5026 레이다 · 6026 위성 (기기당 1개)</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -3904,12 +4001,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>소각</t>
+          <t>표준</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>데이터 판매 시 결제액의 50% 영구 소각</t>
+          <t>XRPL 발행 자산(IOU) · XLS-20 / XLS-30</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -3921,17 +4018,17 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>토큰</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>예산 방식</t>
+          <t>총 발행량</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>에폭(1일) 단위 고정 예산 · 품질 점수 기여도로 배분</t>
+          <t>1,000,000 (고정)</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -3943,17 +4040,17 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>보상</t>
+          <t>토큰</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>기기당 상한</t>
+          <t>소각</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>일 예산의 0.5%</t>
+          <t>데이터 판매 시 결제액의 50% 영구 소각</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -3970,12 +4067,12 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>기기 배수</t>
+          <t>예산 방식</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>ARC-600DA = 기준 1.0</t>
+          <t>에폭(1일) 단위 고정 예산 · 품질 점수 기여도로 배분</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -3992,34 +4089,34 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>수령 조건</t>
+          <t>기기당 상한</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>기기 라이선스 NFT 발급</t>
+          <t>일 예산의 0.5%</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>8/30 회의 · 사이트</t>
+          <t>사이트</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>개인정보</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>비식별화</t>
+          <t>기기 배수</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>위치 일반화 · 시간 집계 · 식별자 회전 · k-익명성 · 속성 일반화</t>
+          <t>ARC-600DA = 기준 1.0</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -4031,39 +4128,39 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>개인정보</t>
+          <t>보상</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>응답 단위</t>
+          <t>수령 조건</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>개별 기기가 아닌 코호트 통계</t>
+          <t>기기 라이선스 NFT 발급</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>사이트</t>
+          <t>8/30 회의 · 사이트</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>기기</t>
+          <t>개인정보</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>모델</t>
+          <t>비식별화</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>ARC-600DA 실내 공기질 측정기</t>
+          <t>위치 일반화 · 시간 집계 · 식별자 회전 · k-익명성 · 속성 일반화</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -4075,17 +4172,17 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>기기</t>
+          <t>개인정보</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>측정 항목</t>
+          <t>응답 단위</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>CO₂ · 미세먼지 · 온습도</t>
+          <t>개별 기기가 아닌 코호트 통계</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -4102,15 +4199,59 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>ARC-600DA 실내 공기질 측정기</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>사이트</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>기기</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>측정 항목</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>CO₂ · 미세먼지 · 온습도</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>사이트</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>기기</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
           <t>인증</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>대한민국 KC 인증 · 성능 인증</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>8/30 서우 확정</t>
         </is>
